--- a/odoo/addons/base/static/xls/contacts_import_template.xlsx
+++ b/odoo/addons/base/static/xls/contacts_import_template.xlsx
@@ -512,7 +512,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Phone Numbers</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
